--- a/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
+++ b/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:49:16+00:00</t>
+    <t>2026-09-16T12:34:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -967,7 +967,7 @@
     <t>Assessment whether this event was of real importance.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-gravite-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-gravite-cisis|20260716085852</t>
   </si>
   <si>
     <t>AdverseEvent.severity</t>
@@ -1109,7 +1109,7 @@
     <t>Assessment of if the entity caused the event.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imputabilite-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imputabilite-cisis|20260716085851</t>
   </si>
   <si>
     <t>AdverseEvent.suspectEntity.causality.productRelatedness</t>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>78</v>

--- a/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
+++ b/nr-doc-core-adverse-event/ig/StructureDefinition-fr-core-adverse-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:34:54+00:00</t>
+    <t>2026-09-17T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>86</v>
